--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="0.0%"/>
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,12 @@
       <name val="Noto Sans TC"/>
       <i val="1"/>
       <color rgb="FF059669"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <b val="1"/>
+      <color rgb="FF888888"/>
       <sz val="10"/>
     </font>
     <font>
@@ -278,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -298,45 +304,48 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -345,58 +354,58 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -477,8 +486,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_10" displayName="ConsensusTbl_10" ref="B10:N11" headerRowCount="1">
-  <autoFilter ref="B10:N11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_11" displayName="ConsensusTbl_11" ref="B11:N12" headerRowCount="1">
+  <autoFilter ref="B11:N12"/>
   <tableColumns count="13">
     <tableColumn id="2" name="#"/>
     <tableColumn id="3" name="代號"/>
@@ -787,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N115"/>
+  <dimension ref="B2:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +832,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 進場關注 9988  |  避開: 今日無除權息  |  訊號: 中性但 hot 多 (27 個信號 — 留意)</t>
+          <t>💡 📌 一般共識 9988 (Q5 中性, 中性信號)  |  避開: 今日無除權息  |  訊號: 中性但 hot 多 (27 個信號 — 留意)</t>
         </is>
       </c>
     </row>
@@ -851,682 +860,662 @@
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ⓘ 排序: 合計淨買金額 ↓  |  ⚠️ 名稱前 = 領頭大戶獨佔 ≥50% (1 人獨大, 真共識訊號被稀釋, hover 名稱看詳細%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>💤 今日無 quad 訊號 (Q5=中性, 無 master 量爆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="B10" s="8" t="inlineStr">
         <is>
+          <t>ⓘ 排序: 合計淨買金額 ↓  |  ⭐ 名稱前 = quad 命中 (Phase 3.2 三訊號齊聚, 預期 78.9% alpha)  |  ⚠️ = 領頭大戶獨佔 ≥50% (假共識防呆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>大戶數</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>分點數</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>領頭大戶</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>領頭金額(萬)</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>#2 大戶</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>#2 金額(萬)</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>#3 大戶</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>#3 金額(萬)</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>+更多</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>合計淨買(萬)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="9" t="n">
+    <row r="12">
+      <c r="B12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>9988</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>強共識股</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>巨人傑</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <v>9900</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Tradow</t>
         </is>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J12" s="15" t="n">
         <v>9800</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L12" s="15" t="n">
         <v>9700</v>
       </c>
-      <c r="M11" s="15" t="n">
+      <c r="M12" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="N11" s="13" t="n">
+      <c r="N12" s="14" t="n">
         <v>94500</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>▍ A. 追蹤池摘要 (10 秒判讀今日 13 位大戶在做什麼)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Q1 活躍率</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Q2 淨買差</t>
         </is>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>37.675</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C16" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>0.2877493082442527</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="22" t="n">
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="23" t="n">
         <v>58.8</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="23" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>✅ 過去 30 天 P/C 命中率: 偏多 4/7 (57%) | 偏空 1/1 (100%) | 整體 5/8 (62%)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>▍ B. Top 5 高手(按今日總買金額)</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>▍ C. Top 5 熱門個股(按今日淨買金額)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>買進(萬元)</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>佔比%</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>個股</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>淨買(萬元)</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>漲跌%</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>民哥</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>79000</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>94500</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="30" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>50200</v>
+        <v>1</v>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>民哥</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>79000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>台積電(2330)</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>42500</v>
-      </c>
-      <c r="I22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="n">
+        <v>94500</v>
+      </c>
+      <c r="I22" s="30" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="n">
-        <v>45600</v>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>50200</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>0.099</v>
+        <v>2</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>台積電(2330)</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>42500</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="n">
-        <v>40800</v>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>45600</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>鴻海(2317)</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>2250</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>0.09849999999999999</v>
+        <v>3</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I24" s="30" t="n">
+        <v>0.099</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>40800</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>鴻海(2317)</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I25" s="30" t="n">
+        <v>0.09849999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D26" s="29" t="n">
         <v>35500</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>8.8%</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="34" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>嚴重度</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>金額/檔數</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>張濬安(航海王)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>張濬安(航海王) 今日買進 14 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>14 檔</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="35" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>竹科主力分點</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>竹科主力分點 今日買進 10 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>10 檔</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
+    <row r="33">
+      <c r="B33" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>蔣承翰</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>蔣承翰 今日買進 10 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>10 檔</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="35" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E33" s="35" t="inlineStr">
+      <c r="E34" s="36" t="inlineStr">
         <is>
           <t>強森 今日買進 9 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="F34" s="36" t="inlineStr">
         <is>
           <t>9 檔</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
+    <row r="35">
+      <c r="B35" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>巨人傑</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>巨人傑 今日買進 8 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>8 檔</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="35" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>陳律師</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>陳律師 今日買進 8 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F36" s="36" t="inlineStr">
         <is>
           <t>8 檔</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
+    <row r="37">
+      <c r="B37" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>布哥/n_nchang</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>布哥/n_nchang 今日買進 7 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>7 檔</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="35" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>民哥</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>民哥 今日買進 6 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="F38" s="36" t="inlineStr">
         <is>
           <t>6 檔</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>🆕 新標的</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>迷你哥/松山哥 今日買進 6 檔新標的 (過去從沒買過)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>6 檔</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>🆕 新標的</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>陳族元</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E39" s="35" t="inlineStr">
-        <is>
-          <t>陳族元 今日買進 6 檔新標的 (過去從沒買過)</t>
-        </is>
-      </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>6 檔</t>
         </is>
@@ -1535,1641 +1524,1669 @@
     <row r="40">
       <c r="B40" s="36" t="inlineStr">
         <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E40" s="36" t="inlineStr">
+        <is>
+          <t>陳族元 今日買進 6 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F40" s="36" t="inlineStr">
+        <is>
+          <t>6 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="37" t="inlineStr">
+        <is>
           <t>… 另 3 筆 anomaly (詳見當日 sheet)</t>
         </is>
       </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="38" t="inlineStr">
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="38" t="n"/>
+      <c r="F41" s="38" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="39" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D43" s="39" t="inlineStr">
+      <c r="D44" s="40" t="inlineStr">
         <is>
           <t>連續天數</t>
         </is>
       </c>
-      <c r="E43" s="39" t="inlineStr">
+      <c r="E44" s="40" t="inlineStr">
         <is>
           <t>累計買金額(萬)</t>
         </is>
       </c>
-      <c r="F43" s="39" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
+    <row r="45">
+      <c r="B45" t="inlineStr">
         <is>
           <t>🔴 陳族元</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2327</t>
         </is>
       </c>
-      <c r="D44" s="40" t="n">
+      <c r="D45" s="41" t="n">
         <v>36</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E45" t="n">
         <v>3622090</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>陳族元 連續 36 天加碼 2327 (累計 3,622,090 萬)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="35" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>🔴 張濬安(航海王)</t>
         </is>
       </c>
-      <c r="C45" s="35" t="inlineStr">
+      <c r="C46" s="36" t="inlineStr">
         <is>
           <t>2327</t>
         </is>
       </c>
-      <c r="D45" s="41" t="n">
+      <c r="D46" s="42" t="n">
         <v>29</v>
       </c>
-      <c r="E45" s="35" t="n">
+      <c r="E46" s="36" t="n">
         <v>2603100</v>
       </c>
-      <c r="F45" s="35" t="inlineStr">
+      <c r="F46" s="36" t="inlineStr">
         <is>
           <t>張濬安(航海王) 連續 29 天加碼 2327 (累計 2,603,100 萬)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
+    <row r="47">
+      <c r="B47" t="inlineStr">
         <is>
           <t>🔴 張濬安(航海王)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>2409</t>
         </is>
       </c>
-      <c r="D46" s="40" t="n">
+      <c r="D47" s="41" t="n">
         <v>24</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>263703</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>張濬安(航海王) 連續 24 天加碼 2409 (累計 263,703 萬)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="35" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>🔴 陳族元</t>
         </is>
       </c>
-      <c r="C47" s="35" t="inlineStr">
+      <c r="C48" s="36" t="inlineStr">
         <is>
           <t>6274</t>
         </is>
       </c>
-      <c r="D47" s="41" t="n">
+      <c r="D48" s="42" t="n">
         <v>23</v>
       </c>
-      <c r="E47" s="35" t="n">
+      <c r="E48" s="36" t="n">
         <v>634278</v>
       </c>
-      <c r="F47" s="35" t="inlineStr">
+      <c r="F48" s="36" t="inlineStr">
         <is>
           <t>陳族元 連續 23 天加碼 6274 (累計 634,278 萬)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="B49" t="inlineStr">
         <is>
           <t>🔴 陳族元</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="D48" s="40" t="n">
+      <c r="D49" s="41" t="n">
         <v>22</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E49" t="n">
         <v>2744015</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>陳族元 連續 22 天加碼 2330 (累計 2,744,015 萬)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="42" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="43" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>今日總買(萬)</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>Top1 個股</t>
         </is>
       </c>
-      <c r="E51" s="43" t="inlineStr">
+      <c r="E52" s="44" t="inlineStr">
         <is>
           <t>Top1 金額</t>
         </is>
       </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="F52" s="44" t="inlineStr">
         <is>
           <t>Top2 個股</t>
         </is>
       </c>
-      <c r="G51" s="43" t="inlineStr">
+      <c r="G52" s="44" t="inlineStr">
         <is>
           <t>Top2 金額</t>
         </is>
       </c>
-      <c r="H51" s="43" t="inlineStr">
+      <c r="H52" s="44" t="inlineStr">
         <is>
           <t>Top3 個股</t>
         </is>
       </c>
-      <c r="I51" s="43" t="inlineStr">
+      <c r="I52" s="44" t="inlineStr">
         <is>
           <t>Top3 金額</t>
         </is>
       </c>
-      <c r="J51" s="43" t="inlineStr">
+      <c r="J52" s="44" t="inlineStr">
         <is>
           <t>Top3 合計%</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="27" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>🔥 民哥</t>
         </is>
       </c>
-      <c r="C52" s="28" t="n">
+      <c r="C53" s="29" t="n">
         <v>59000</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E52" s="28" t="n">
+      <c r="E53" s="29" t="n">
         <v>40000</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G52" s="28" t="n">
+      <c r="G53" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>聯發科(2454)</t>
         </is>
       </c>
-      <c r="I52" s="28" t="n">
+      <c r="I53" s="29" t="n">
         <v>9000</v>
       </c>
-      <c r="J52" s="44" t="n">
+      <c r="J53" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="31" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>🔥 林滄海</t>
         </is>
       </c>
-      <c r="C53" s="28" t="n">
+      <c r="C54" s="29" t="n">
         <v>25600</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E53" s="28" t="n">
+      <c r="E54" s="29" t="n">
         <v>12500</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G53" s="28" t="n">
+      <c r="G54" s="29" t="n">
         <v>10100</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>鴻海(2317)</t>
         </is>
       </c>
-      <c r="I53" s="28" t="n">
+      <c r="I54" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="J53" s="44" t="n">
+      <c r="J54" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="33" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="34" t="inlineStr">
         <is>
           <t>🔥 迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="C54" s="28" t="n">
+      <c r="C55" s="29" t="n">
         <v>15500</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E54" s="28" t="n">
+      <c r="E55" s="29" t="n">
         <v>10500</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="G54" s="28" t="n">
+      <c r="G55" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="J54" s="44" t="n">
+      <c r="J55" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="45" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="46" t="inlineStr">
         <is>
           <t>🔥 巨人傑</t>
         </is>
       </c>
-      <c r="C55" s="28" t="n">
+      <c r="C56" s="29" t="n">
         <v>10900</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E55" s="28" t="n">
+      <c r="E56" s="29" t="n">
         <v>10900</v>
       </c>
-      <c r="J55" s="44" t="n">
+      <c r="J56" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="32" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="33" t="inlineStr">
         <is>
           <t>🔥 Tradow</t>
         </is>
       </c>
-      <c r="C56" s="28" t="n">
+      <c r="C57" s="29" t="n">
         <v>10800</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E56" s="28" t="n">
+      <c r="E57" s="29" t="n">
         <v>10800</v>
       </c>
-      <c r="J56" s="44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="46" t="inlineStr">
-        <is>
-          <t>🔥 強森</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="n">
-        <v>10700</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E57" s="28" t="n">
-        <v>10700</v>
-      </c>
-      <c r="J57" s="44" t="n">
+      <c r="J57" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>🔥 布哥/n_nchang</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="n">
-        <v>10600</v>
+          <t>🔥 強森</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>10700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E58" s="28" t="n">
-        <v>10600</v>
-      </c>
-      <c r="J58" s="44" t="n">
+      <c r="E58" s="29" t="n">
+        <v>10700</v>
+      </c>
+      <c r="J58" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="48" t="inlineStr">
         <is>
-          <t>🔥 陳律師</t>
-        </is>
-      </c>
-      <c r="C59" s="28" t="n">
-        <v>10400</v>
+          <t>🔥 布哥/n_nchang</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>10600</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E59" s="28" t="n">
-        <v>10400</v>
-      </c>
-      <c r="J59" s="44" t="n">
+      <c r="E59" s="29" t="n">
+        <v>10600</v>
+      </c>
+      <c r="J59" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="49" t="inlineStr">
         <is>
+          <t>🔥 陳律師</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="n">
+        <v>10400</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="n">
+        <v>10400</v>
+      </c>
+      <c r="J60" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="50" t="inlineStr">
+        <is>
           <t>🔥 陳族元</t>
         </is>
       </c>
-      <c r="C60" s="28" t="n">
+      <c r="C61" s="29" t="n">
         <v>10300</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E60" s="28" t="n">
+      <c r="E61" s="29" t="n">
         <v>10300</v>
       </c>
-      <c r="J60" s="44" t="n">
+      <c r="J61" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="30" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>🔥 張濬安(航海王)</t>
         </is>
       </c>
-      <c r="C61" s="28" t="n">
+      <c r="C62" s="29" t="n">
         <v>10200</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E61" s="28" t="n">
+      <c r="E62" s="29" t="n">
         <v>10200</v>
       </c>
-      <c r="J61" s="44" t="n">
+      <c r="J62" s="45" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="B63" s="50" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="51" t="inlineStr">
         <is>
           <t>▍ G. 注意股 (資料日 20260625)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="51" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="52" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C64" s="51" t="inlineStr">
+      <c r="C65" s="52" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D64" s="51" t="inlineStr">
+      <c r="D65" s="52" t="inlineStr">
         <is>
           <t>累計次數</t>
         </is>
       </c>
-      <c r="E64" s="51" t="inlineStr">
+      <c r="E65" s="52" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="F64" s="51" t="inlineStr">
+      <c r="F65" s="52" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
+    <row r="66">
+      <c r="B66" t="inlineStr">
         <is>
           <t>050328</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>華固凱基56購01</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>25</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="35" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="36" t="inlineStr">
         <is>
           <t>058153</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C67" s="36" t="inlineStr">
         <is>
           <t>SGBR2X元大59購04</t>
         </is>
       </c>
-      <c r="D66" s="35" t="n">
+      <c r="D67" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="35" t="n">
+      <c r="E67" s="36" t="n">
         <v>1.34</v>
       </c>
-      <c r="F66" s="35" t="inlineStr">
+      <c r="F67" s="36" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
+    <row r="68">
+      <c r="B68" t="inlineStr">
         <is>
           <t>085788</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>T50反1中信5C購01</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E68" t="n">
         <v>1.33</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="35" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="36" t="inlineStr">
         <is>
           <t>087327</t>
         </is>
       </c>
-      <c r="C68" s="35" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
         <is>
           <t>台積電凱基67購02</t>
         </is>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D69" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="35" t="n">
+      <c r="E69" s="36" t="n">
         <v>21.4</v>
       </c>
-      <c r="F68" s="35" t="inlineStr">
+      <c r="F69" s="36" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
+    <row r="70">
+      <c r="B70" t="inlineStr">
         <is>
           <t>1435</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>中福</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E70" t="n">
         <v>20.6</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="35" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="36" t="inlineStr">
         <is>
           <t>2233</t>
         </is>
       </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="C71" s="36" t="inlineStr">
         <is>
           <t>宇隆</t>
         </is>
       </c>
-      <c r="D70" s="35" t="n">
+      <c r="D71" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="35" t="n">
+      <c r="E71" s="36" t="n">
         <v>230.5</v>
       </c>
-      <c r="F70" s="35" t="inlineStr">
+      <c r="F71" s="36" t="inlineStr">
         <is>
           <t>36.76</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
+    <row r="72">
+      <c r="B72" t="inlineStr">
         <is>
           <t>2303</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E72" t="n">
         <v>178.5</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>44.85</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="35" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="36" t="inlineStr">
         <is>
           <t>2316</t>
         </is>
       </c>
-      <c r="C72" s="35" t="inlineStr">
+      <c r="C73" s="36" t="inlineStr">
         <is>
           <t>楠梓電</t>
         </is>
       </c>
-      <c r="D72" s="35" t="n">
+      <c r="D73" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="35" t="n">
+      <c r="E73" s="36" t="n">
         <v>234.5</v>
       </c>
-      <c r="F72" s="35" t="inlineStr">
+      <c r="F73" s="36" t="inlineStr">
         <is>
           <t>15.19</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
+    <row r="74">
+      <c r="B74" t="inlineStr">
         <is>
           <t>2383</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E74" t="n">
         <v>5640</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>122.34</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="35" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="36" t="inlineStr">
         <is>
           <t>2481</t>
         </is>
       </c>
-      <c r="C74" s="35" t="inlineStr">
+      <c r="C75" s="36" t="inlineStr">
         <is>
           <t>強茂</t>
         </is>
       </c>
-      <c r="D74" s="35" t="n">
+      <c r="D75" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="35" t="n">
+      <c r="E75" s="36" t="n">
         <v>192</v>
       </c>
-      <c r="F74" s="35" t="inlineStr">
+      <c r="F75" s="36" t="inlineStr">
         <is>
           <t>60.95</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
+    <row r="76">
+      <c r="B76" t="inlineStr">
         <is>
           <t>2483</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>百容</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>50.7</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>55.11</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="35" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="36" t="inlineStr">
         <is>
           <t>2484</t>
         </is>
       </c>
-      <c r="C76" s="35" t="inlineStr">
+      <c r="C77" s="36" t="inlineStr">
         <is>
           <t>希華</t>
         </is>
       </c>
-      <c r="D76" s="35" t="n">
+      <c r="D77" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="35" t="n">
+      <c r="E77" s="36" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="F76" s="35" t="inlineStr">
+      <c r="F77" s="36" t="inlineStr">
         <is>
           <t>94.46</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
+    <row r="78">
+      <c r="B78" t="inlineStr">
         <is>
           <t>3189</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>景碩</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E78" t="n">
         <v>812</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>228.73</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="35" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="36" t="inlineStr">
         <is>
           <t>3481</t>
         </is>
       </c>
-      <c r="C78" s="35" t="inlineStr">
+      <c r="C79" s="36" t="inlineStr">
         <is>
           <t>群創</t>
         </is>
       </c>
-      <c r="D78" s="35" t="n">
+      <c r="D79" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="35" t="n">
+      <c r="E79" s="36" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="F78" s="35" t="inlineStr">
+      <c r="F79" s="36" t="inlineStr">
         <is>
           <t>644.55</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
+    <row r="80">
+      <c r="B80" t="inlineStr">
         <is>
           <t>3653</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E80" t="n">
         <v>3390</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>93.78</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="B81" s="4" t="inlineStr">
+    <row r="82" ht="22" customHeight="1">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260625)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="8" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>借券張數</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>融券張數</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
+    <row r="84">
+      <c r="B84" t="inlineStr">
         <is>
           <t>3481</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>群創</t>
         </is>
       </c>
-      <c r="D83" s="28" t="n">
+      <c r="D84" s="29" t="n">
         <v>44667</v>
       </c>
-      <c r="E83" s="28" t="n">
+      <c r="E84" s="29" t="n">
         <v>1292</v>
       </c>
-      <c r="F83" s="52" t="n">
+      <c r="F84" s="53" t="n">
         <v>34.57</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="35" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="36" t="inlineStr">
         <is>
           <t>2312</t>
         </is>
       </c>
-      <c r="C84" s="35" t="inlineStr">
+      <c r="C85" s="36" t="inlineStr">
         <is>
           <t>金寶</t>
         </is>
       </c>
-      <c r="D84" s="53" t="n">
+      <c r="D85" s="54" t="n">
         <v>13586</v>
       </c>
-      <c r="E84" s="53" t="n">
+      <c r="E85" s="54" t="n">
         <v>51</v>
       </c>
-      <c r="F84" s="54" t="n">
+      <c r="F85" s="55" t="n">
         <v>266.39</v>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
+    <row r="86">
+      <c r="B86" t="inlineStr">
         <is>
           <t>2880</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>華南金</t>
         </is>
       </c>
-      <c r="D85" s="28" t="n">
+      <c r="D86" s="29" t="n">
         <v>12943</v>
       </c>
-      <c r="E85" s="28" t="n">
+      <c r="E86" s="29" t="n">
         <v>1617</v>
       </c>
-      <c r="F85" s="52" t="n">
+      <c r="F86" s="53" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="35" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="36" t="inlineStr">
         <is>
           <t>2884</t>
         </is>
       </c>
-      <c r="C86" s="35" t="inlineStr">
+      <c r="C87" s="36" t="inlineStr">
         <is>
           <t>玉山金</t>
         </is>
       </c>
-      <c r="D86" s="53" t="n">
+      <c r="D87" s="54" t="n">
         <v>10650</v>
       </c>
-      <c r="E86" s="53" t="n">
+      <c r="E87" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="35" t="inlineStr">
+      <c r="F87" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="40" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="41" t="inlineStr">
         <is>
           <t>🔴 009816</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>凱基台灣TOP50</t>
         </is>
       </c>
-      <c r="D87" s="28" t="n">
+      <c r="D88" s="29" t="n">
         <v>8563</v>
       </c>
-      <c r="E87" s="28" t="n">
+      <c r="E88" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="F87" s="55" t="n">
+      <c r="F88" s="56" t="n">
         <v>2854.33</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="35" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="36" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
       </c>
-      <c r="C88" s="35" t="inlineStr">
+      <c r="C89" s="36" t="inlineStr">
         <is>
           <t>主動統一台股增長</t>
         </is>
       </c>
-      <c r="D88" s="53" t="n">
+      <c r="D89" s="54" t="n">
         <v>7023</v>
       </c>
-      <c r="E88" s="53" t="n">
+      <c r="E89" s="54" t="n">
         <v>102</v>
       </c>
-      <c r="F88" s="54" t="n">
+      <c r="F89" s="55" t="n">
         <v>68.84999999999999</v>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
+    <row r="90">
+      <c r="B90" t="inlineStr">
         <is>
           <t>2887</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>台新新光金</t>
         </is>
       </c>
-      <c r="D89" s="28" t="n">
+      <c r="D90" s="29" t="n">
         <v>6286</v>
       </c>
-      <c r="E89" s="28" t="n">
+      <c r="E90" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="35" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="36" t="inlineStr">
         <is>
           <t>4938</t>
         </is>
       </c>
-      <c r="C90" s="35" t="inlineStr">
+      <c r="C91" s="36" t="inlineStr">
         <is>
           <t>和碩</t>
         </is>
       </c>
-      <c r="D90" s="53" t="n">
+      <c r="D91" s="54" t="n">
         <v>6112</v>
       </c>
-      <c r="E90" s="53" t="n">
+      <c r="E91" s="54" t="n">
         <v>21</v>
       </c>
-      <c r="F90" s="54" t="n">
+      <c r="F91" s="55" t="n">
         <v>291.05</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
+    <row r="92">
+      <c r="B92" t="inlineStr">
         <is>
           <t>2890</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>永豐金</t>
         </is>
       </c>
-      <c r="D91" s="28" t="n">
+      <c r="D92" s="29" t="n">
         <v>5641</v>
       </c>
-      <c r="E91" s="28" t="n">
+      <c r="E92" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="35" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="36" t="inlineStr">
         <is>
           <t>9904</t>
         </is>
       </c>
-      <c r="C92" s="35" t="inlineStr">
+      <c r="C93" s="36" t="inlineStr">
         <is>
           <t>寶成</t>
         </is>
       </c>
-      <c r="D92" s="53" t="n">
+      <c r="D93" s="54" t="n">
         <v>5221</v>
       </c>
-      <c r="E92" s="53" t="n">
+      <c r="E93" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F92" s="35" t="inlineStr">
+      <c r="F93" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
+    <row r="94">
+      <c r="B94" t="inlineStr">
         <is>
           <t>2303</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="D93" s="28" t="n">
+      <c r="D94" s="29" t="n">
         <v>5158</v>
       </c>
-      <c r="E93" s="28" t="n">
+      <c r="E94" s="29" t="n">
         <v>198</v>
       </c>
-      <c r="F93" s="52" t="n">
+      <c r="F94" s="53" t="n">
         <v>26.05</v>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="35" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="36" t="inlineStr">
         <is>
           <t>1605</t>
         </is>
       </c>
-      <c r="C94" s="35" t="inlineStr">
+      <c r="C95" s="36" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="D94" s="53" t="n">
+      <c r="D95" s="54" t="n">
         <v>4356</v>
       </c>
-      <c r="E94" s="53" t="n">
+      <c r="E95" s="54" t="n">
         <v>42</v>
       </c>
-      <c r="F94" s="54" t="n">
+      <c r="F95" s="55" t="n">
         <v>103.71</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="40" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="41" t="inlineStr">
         <is>
           <t>🔴 1216</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>統一</t>
         </is>
       </c>
-      <c r="D95" s="28" t="n">
+      <c r="D96" s="29" t="n">
         <v>4269</v>
       </c>
-      <c r="E95" s="28" t="n">
+      <c r="E96" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="F95" s="55" t="n">
+      <c r="F96" s="56" t="n">
         <v>1423</v>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="35" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="36" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="C96" s="35" t="inlineStr">
+      <c r="C97" s="36" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="D96" s="53" t="n">
+      <c r="D97" s="54" t="n">
         <v>4231</v>
       </c>
-      <c r="E96" s="53" t="n">
+      <c r="E97" s="54" t="n">
         <v>135</v>
       </c>
-      <c r="F96" s="54" t="n">
+      <c r="F97" s="55" t="n">
         <v>31.34</v>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
+    <row r="98">
+      <c r="B98" t="inlineStr">
         <is>
           <t>5876</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>上海商銀</t>
         </is>
       </c>
-      <c r="D97" s="28" t="n">
+      <c r="D98" s="29" t="n">
         <v>4209</v>
       </c>
-      <c r="E97" s="28" t="n">
+      <c r="E98" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="B99" s="56" t="inlineStr">
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="57" t="inlineStr">
         <is>
           <t>▍ I. 未來 30 天除權息 (有效 257 檔, 已剔除過期)</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="51" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="52" t="inlineStr">
         <is>
           <t>除權息日</t>
         </is>
       </c>
-      <c r="C100" s="51" t="inlineStr">
+      <c r="C101" s="52" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="D100" s="51" t="inlineStr">
+      <c r="D101" s="52" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="E100" s="51" t="inlineStr">
+      <c r="E101" s="52" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="F100" s="51" t="inlineStr">
+      <c r="F101" s="52" t="inlineStr">
         <is>
           <t>現金股利</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" t="inlineStr">
+    <row r="102">
+      <c r="B102" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>1525</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>江申</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F101" t="n">
+      <c r="F102" t="n">
         <v>2.8</v>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="35" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C102" s="35" t="inlineStr">
+      <c r="C103" s="36" t="inlineStr">
         <is>
           <t>2362</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
+      <c r="D103" s="36" t="inlineStr">
         <is>
           <t>藍天</t>
         </is>
       </c>
-      <c r="E102" s="35" t="inlineStr">
+      <c r="E103" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F102" s="35" t="n">
+      <c r="F103" s="36" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
+    <row r="104">
+      <c r="B104" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>2432</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>倚天酷碁-創</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F103" t="n">
+      <c r="F104" t="n">
         <v>1.7</v>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="35" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C104" s="35" t="inlineStr">
+      <c r="C105" s="36" t="inlineStr">
         <is>
           <t>2451</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
+      <c r="D105" s="36" t="inlineStr">
         <is>
           <t>創見</t>
         </is>
       </c>
-      <c r="E104" s="35" t="inlineStr">
+      <c r="E105" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F104" s="35" t="n">
+      <c r="F105" s="36" t="n">
         <v>11.782382</v>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" t="inlineStr">
+    <row r="106">
+      <c r="B106" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2489</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>瑞軒</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F105" t="n">
+      <c r="F106" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="35" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C106" s="35" t="inlineStr">
+      <c r="C107" s="36" t="inlineStr">
         <is>
           <t>3046</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
+      <c r="D107" s="36" t="inlineStr">
         <is>
           <t>建碁</t>
         </is>
       </c>
-      <c r="E106" s="35" t="inlineStr">
+      <c r="E107" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F106" s="35" t="n">
+      <c r="F107" s="36" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" t="inlineStr">
+    <row r="108">
+      <c r="B108" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>3338</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>泰碩</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F107" t="n">
+      <c r="F108" t="n">
         <v>1.3</v>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="35" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C108" s="35" t="inlineStr">
+      <c r="C109" s="36" t="inlineStr">
         <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D109" s="36" t="inlineStr">
         <is>
           <t>茂林-KY</t>
         </is>
       </c>
-      <c r="E108" s="35" t="inlineStr">
+      <c r="E109" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F108" s="35" t="n">
+      <c r="F109" s="36" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" t="inlineStr">
+    <row r="110">
+      <c r="B110" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>5285</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>界霖</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F109" t="n">
+      <c r="F110" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="35" t="inlineStr">
+    <row r="111">
+      <c r="B111" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C110" s="35" t="inlineStr">
+      <c r="C111" s="36" t="inlineStr">
         <is>
           <t>5515</t>
         </is>
       </c>
-      <c r="D110" s="35" t="inlineStr">
+      <c r="D111" s="36" t="inlineStr">
         <is>
           <t>建國</t>
         </is>
       </c>
-      <c r="E110" s="35" t="inlineStr">
+      <c r="E111" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F110" s="35" t="n">
+      <c r="F111" s="36" t="n">
         <v>3.3</v>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" t="inlineStr">
+    <row r="112">
+      <c r="B112" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>5521</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>工信</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F111" t="n">
+      <c r="F112" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="35" t="inlineStr">
+    <row r="113">
+      <c r="B113" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C112" s="35" t="inlineStr">
+      <c r="C113" s="36" t="inlineStr">
         <is>
           <t>5522</t>
         </is>
       </c>
-      <c r="D112" s="35" t="inlineStr">
+      <c r="D113" s="36" t="inlineStr">
         <is>
           <t>遠雄</t>
         </is>
       </c>
-      <c r="E112" s="35" t="inlineStr">
+      <c r="E113" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F112" s="35" t="n">
+      <c r="F113" s="36" t="n">
         <v>5.5</v>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" t="inlineStr">
+    <row r="114">
+      <c r="B114" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>6189</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>豐藝</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F113" t="n">
+      <c r="F114" t="n">
         <v>2.699525</v>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="35" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="36" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C114" s="35" t="inlineStr">
+      <c r="C115" s="36" t="inlineStr">
         <is>
           <t>6205</t>
         </is>
       </c>
-      <c r="D114" s="35" t="inlineStr">
+      <c r="D115" s="36" t="inlineStr">
         <is>
           <t>詮欣</t>
         </is>
       </c>
-      <c r="E114" s="35" t="inlineStr">
+      <c r="E115" s="36" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F114" s="35" t="n">
+      <c r="F115" s="36" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" t="inlineStr">
+    <row r="116">
+      <c r="B116" t="inlineStr">
         <is>
           <t>20260625</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>6585</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>鼎基</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F115" t="n">
+      <c r="F116" t="n">
         <v>4.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B7:N7"/>
-    <mergeCell ref="F19:I19"/>
     <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B16:N16"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="B18:N18"/>
+    <mergeCell ref="F20:I20"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B81:J81"/>
+    <mergeCell ref="B100:J100"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B17:N17"/>
-    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B10:N10"/>
   </mergeCells>
-  <conditionalFormatting sqref="N11">
+  <conditionalFormatting sqref="N12">
     <cfRule type="dataBar" priority="1">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3178,7 +3195,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
+  <conditionalFormatting sqref="E12">
     <cfRule type="dataBar" priority="2">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3187,7 +3204,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21:D25">
+  <conditionalFormatting sqref="D22:D26">
     <cfRule type="dataBar" priority="3">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3196,7 +3213,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H25">
+  <conditionalFormatting sqref="H22:H26">
     <cfRule type="dataBar" priority="4">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3205,7 +3222,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:D48">
+  <conditionalFormatting sqref="D45:D49">
     <cfRule type="dataBar" priority="5">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3214,7 +3231,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44:E48">
+  <conditionalFormatting sqref="E45:E49">
     <cfRule type="dataBar" priority="6">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3223,7 +3240,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C52:C61">
+  <conditionalFormatting sqref="C53:C62">
     <cfRule type="dataBar" priority="7">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3232,7 +3249,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52:J61">
+  <conditionalFormatting sqref="J53:J62">
     <cfRule type="dataBar" priority="8">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3241,7 +3258,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D65:D79">
+  <conditionalFormatting sqref="D66:D80">
     <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3250,7 +3267,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D83:D97">
+  <conditionalFormatting sqref="D84:D98">
     <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -3259,7 +3276,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F83:F97">
+  <conditionalFormatting sqref="F84:F98">
     <cfRule type="dataBar" priority="11">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>

--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -853,7 +853,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% (n=38, mean +4.37%) vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
+          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
         </is>
       </c>
     </row>

--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -853,7 +853,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
+          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
         </is>
       </c>
     </row>

--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -853,7 +853,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
+          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 85.7% [70.6–93.7% 95% CI] (n=35, mean +4.75%) | 30d 實戰: 11/14 = 78.6% vs baseline 45.2% = +40.5pp — 強 alpha (p&lt;0.001)</t>
         </is>
       </c>
     </row>

--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -853,7 +853,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 85.7% [70.6–93.7% 95% CI] (n=35, mean +4.75%) | 30d 實戰: 11/14 = 78.6% vs baseline 45.2% = +40.5pp — 強 alpha (p&lt;0.001)</t>
+          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 44.1% = +34.8pp — 強 alpha (p&lt;0.001)</t>
         </is>
       </c>
     </row>

--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="0.0%"/>
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,12 @@
       <name val="Noto Sans TC"/>
       <i val="1"/>
       <color rgb="FF6366F1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <i val="1"/>
+      <color rgb="FFB45309"/>
       <sz val="10"/>
     </font>
     <font>
@@ -295,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -324,45 +330,48 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -371,55 +380,55 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="18" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -500,8 +509,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_14" displayName="ConsensusTbl_14" ref="B14:N15" headerRowCount="1">
-  <autoFilter ref="B14:N15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConsensusTbl_15" displayName="ConsensusTbl_15" ref="B15:N16" headerRowCount="1">
+  <autoFilter ref="B15:N16"/>
   <tableColumns count="13">
     <tableColumn id="2" name="#"/>
     <tableColumn id="3" name="代號"/>
@@ -810,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N105"/>
+  <dimension ref="B2:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -839,14 +848,14 @@
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🎯 1 強共識 / Q5 ↕ 中性 58.8% / E 0 異常 / F 0 長期 / J 10 集中 / H 4 借券壓力</t>
+          <t>🎯 1 強共識 / Q5 ↕ 中性 58.7% / E 0 異常 / F 0 長期 / J 10 集中 / H 6 借券壓力</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 9988 (Q5 中性, 中性信號)  |  避開 — 明日恐處置 10 檔: 1435/2233/2302...  |  訊號: 中性但 hot 多 (14 個信號 — 留意)</t>
+          <t>💡 📌 一般共識 9988 (Q5 中性, 中性信號)  |  避開 — 明日恐處置 5 檔: 3189/6213/8021...  |  訊號: 中性但 hot 多 (16 個信號 — 留意)</t>
         </is>
       </c>
     </row>
@@ -867,7 +876,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 43.4% = +35.5pp — 強 alpha (p&lt;0.001)</t>
+          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 45.1% = +33.9pp — 強 alpha (p&lt;0.001)</t>
         </is>
       </c>
     </row>
@@ -902,1946 +911,1954 @@
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="10" t="inlineStr">
         <is>
+          <t>📌 大牌分析師 歷史 alpha: 全 picks n=1461 hit_1d=48% / hit_3d=51%  |  新標 n=302 hit_3d=49% mean=+0.96%  |  連加 n=69 hit_5d=59% mean=+3.86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
           <t>ⓘ 排序: 合計淨買金額 ↓  |  ⭐⭐ = premium quad (陳律師/竹科主力/陳族元, ≥77% hit)  |  ⭐ = 一般 quad (78.9%)  |  ⚠️ = 領頭獨佔 ≥50%  |  🔁 = 過去 7 天 quad 重複  |  📌 = 你關注的 master (大牌分析師) 參與</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>大戶數</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>分點數</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>領頭大戶</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>領頭金額(萬)</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>#2 大戶</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>#2 金額(萬)</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>#3 大戶</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>#3 金額(萬)</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>+更多</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>合計淨買(萬)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="12" t="n">
+    <row r="16">
+      <c r="B16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>9988</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>強共識股</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>巨人傑</t>
         </is>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H16" s="17" t="n">
         <v>9900</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Tradow</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J16" s="18" t="n">
         <v>9800</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>強森</t>
         </is>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L16" s="18" t="n">
         <v>9700</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M16" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N15" s="16" t="n">
+      <c r="N16" s="17" t="n">
         <v>94500</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="19" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>▍ A. 追蹤池摘要 (10 秒判讀今日 13 位大戶在做什麼)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="20" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Q1 活躍率</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C19" s="22" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>Q2 淨買差</t>
         </is>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G19" s="23" t="n">
         <v>37.675</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="20" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Q3 強共識股</t>
         </is>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>Q4 追蹤佔比</t>
         </is>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>0.2877493082442527</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="25" t="n">
-        <v>58.8</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>✅ 過去 30 天 P/C 命中率: 偏多 6/9 (67%) | 偏空 1/1 (100%) | 整體 7/10 (70%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="27" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="26" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>✅ 過去 30 天 P/C 命中率: 偏多 18/28 (64%) | 偏空 0/0 (0%) | 整體 18/28 (64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>▍ B. Top 5 高手(按今日總買金額)</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>▍ C. Top 5 熱門個股(按今日淨買金額)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="29" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>買進(萬元)</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>佔比%</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>個股</t>
         </is>
       </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>淨買(萬元)</t>
         </is>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
         <is>
           <t>漲跌%</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>民哥</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="n">
-        <v>79000</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="H25" s="31" t="n">
-        <v>94500</v>
-      </c>
-      <c r="I25" s="32" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="n">
-        <v>50200</v>
+        <v>1</v>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>民哥</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>79000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>台積電(2330)</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="n">
-        <v>42500</v>
-      </c>
-      <c r="I26" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="H26" s="32" t="n">
+        <v>94500</v>
+      </c>
+      <c r="I26" s="33" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>林滄海</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>45600</v>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>50200</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>聯發科(2454)</t>
-        </is>
-      </c>
-      <c r="H27" s="31" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I27" s="32" t="n">
-        <v>0.099</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>台積電(2330)</t>
+        </is>
+      </c>
+      <c r="H27" s="32" t="n">
+        <v>42500</v>
+      </c>
+      <c r="I27" s="33" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>Tradow</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>40800</v>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>45600</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>鴻海(2317)</t>
-        </is>
-      </c>
-      <c r="H28" s="31" t="n">
-        <v>2250</v>
-      </c>
-      <c r="I28" s="32" t="n">
-        <v>0.09849999999999999</v>
+        <v>3</v>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>聯發科(2454)</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I28" s="33" t="n">
+        <v>0.099</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>40800</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>鴻海(2317)</t>
+        </is>
+      </c>
+      <c r="H29" s="32" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I29" s="33" t="n">
+        <v>0.09849999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D30" s="32" t="n">
         <v>35500</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>8.8%</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="37" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>▍ E. 異常行為警報 (z&gt;2σ 量爆 + 新標的進場)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>嚴重度</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>金額/檔數</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
+    <row r="35">
+      <c r="B35" t="inlineStr">
         <is>
           <t>✅ 今日無異常行為 (追蹤範圍內)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="38" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="39" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="C37" s="39" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D37" s="39" t="inlineStr">
+      <c r="D38" s="40" t="inlineStr">
         <is>
           <t>連續天數</t>
         </is>
       </c>
-      <c r="E37" s="39" t="inlineStr">
+      <c r="E38" s="40" t="inlineStr">
         <is>
           <t>累計買金額(萬)</t>
         </is>
       </c>
-      <c r="F37" s="39" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>尚無連續囤貨紀錄 (追蹤範圍內)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="40" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="41" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="42" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="C41" s="41" t="inlineStr">
+      <c r="C42" s="42" t="inlineStr">
         <is>
           <t>今日總買(萬)</t>
         </is>
       </c>
-      <c r="D41" s="41" t="inlineStr">
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>Top1 個股</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr">
+      <c r="E42" s="42" t="inlineStr">
         <is>
           <t>Top1 金額</t>
         </is>
       </c>
-      <c r="F41" s="41" t="inlineStr">
+      <c r="F42" s="42" t="inlineStr">
         <is>
           <t>Top2 個股</t>
         </is>
       </c>
-      <c r="G41" s="41" t="inlineStr">
+      <c r="G42" s="42" t="inlineStr">
         <is>
           <t>Top2 金額</t>
         </is>
       </c>
-      <c r="H41" s="41" t="inlineStr">
+      <c r="H42" s="42" t="inlineStr">
         <is>
           <t>Top3 個股</t>
         </is>
       </c>
-      <c r="I41" s="41" t="inlineStr">
+      <c r="I42" s="42" t="inlineStr">
         <is>
           <t>Top3 金額</t>
         </is>
       </c>
-      <c r="J41" s="41" t="inlineStr">
+      <c r="J42" s="42" t="inlineStr">
         <is>
           <t>Top3 合計%</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="30" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>🔥 民哥</t>
         </is>
       </c>
-      <c r="C42" s="31" t="n">
+      <c r="C43" s="32" t="n">
         <v>59000</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E42" s="31" t="n">
+      <c r="E43" s="32" t="n">
         <v>40000</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G42" s="31" t="n">
+      <c r="G43" s="32" t="n">
         <v>10000</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>聯發科(2454)</t>
         </is>
       </c>
-      <c r="I42" s="31" t="n">
+      <c r="I43" s="32" t="n">
         <v>9000</v>
       </c>
-      <c r="J42" s="42" t="n">
+      <c r="J43" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="34" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>🔥 林滄海</t>
         </is>
       </c>
-      <c r="C43" s="31" t="n">
+      <c r="C44" s="32" t="n">
         <v>25600</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E43" s="31" t="n">
+      <c r="E44" s="32" t="n">
         <v>12500</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G43" s="31" t="n">
+      <c r="G44" s="32" t="n">
         <v>10100</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>鴻海(2317)</t>
         </is>
       </c>
-      <c r="I43" s="31" t="n">
+      <c r="I44" s="32" t="n">
         <v>3000</v>
       </c>
-      <c r="J43" s="42" t="n">
+      <c r="J44" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="36" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>🔥 迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="C44" s="31" t="n">
+      <c r="C45" s="32" t="n">
         <v>15500</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E44" s="31" t="n">
+      <c r="E45" s="32" t="n">
         <v>10500</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="G44" s="31" t="n">
+      <c r="G45" s="32" t="n">
         <v>5000</v>
       </c>
-      <c r="J44" s="42" t="n">
+      <c r="J45" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="43" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="44" t="inlineStr">
         <is>
           <t>🔥 巨人傑</t>
         </is>
       </c>
-      <c r="C45" s="31" t="n">
+      <c r="C46" s="32" t="n">
         <v>10900</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E45" s="31" t="n">
+      <c r="E46" s="32" t="n">
         <v>10900</v>
       </c>
-      <c r="J45" s="42" t="n">
+      <c r="J46" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="35" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>🔥 Tradow</t>
         </is>
       </c>
-      <c r="C46" s="31" t="n">
+      <c r="C47" s="32" t="n">
         <v>10800</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E46" s="31" t="n">
+      <c r="E47" s="32" t="n">
         <v>10800</v>
       </c>
-      <c r="J46" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="44" t="inlineStr">
-        <is>
-          <t>🔥 強森</t>
-        </is>
-      </c>
-      <c r="C47" s="31" t="n">
-        <v>10700</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="n">
-        <v>10700</v>
-      </c>
-      <c r="J47" s="42" t="n">
+      <c r="J47" s="43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="45" t="inlineStr">
         <is>
-          <t>🔥 布哥/n_nchang</t>
-        </is>
-      </c>
-      <c r="C48" s="31" t="n">
-        <v>10600</v>
+          <t>🔥 強森</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>10700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E48" s="31" t="n">
-        <v>10600</v>
-      </c>
-      <c r="J48" s="42" t="n">
+      <c r="E48" s="32" t="n">
+        <v>10700</v>
+      </c>
+      <c r="J48" s="43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>🔥 陳律師</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="n">
-        <v>10400</v>
+          <t>🔥 布哥/n_nchang</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="n">
+        <v>10600</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E49" s="31" t="n">
-        <v>10400</v>
-      </c>
-      <c r="J49" s="42" t="n">
+      <c r="E49" s="32" t="n">
+        <v>10600</v>
+      </c>
+      <c r="J49" s="43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="47" t="inlineStr">
         <is>
+          <t>🔥 陳律師</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="n">
+        <v>10400</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E50" s="32" t="n">
+        <v>10400</v>
+      </c>
+      <c r="J50" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="48" t="inlineStr">
+        <is>
           <t>🔥 陳族元</t>
         </is>
       </c>
-      <c r="C50" s="31" t="n">
+      <c r="C51" s="32" t="n">
         <v>10300</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E51" s="32" t="n">
         <v>10300</v>
       </c>
-      <c r="J50" s="42" t="n">
+      <c r="J51" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="33" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="34" t="inlineStr">
         <is>
           <t>🔥 張濬安(航海王)</t>
         </is>
       </c>
-      <c r="C51" s="31" t="n">
+      <c r="C52" s="32" t="n">
         <v>10200</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E51" s="31" t="n">
+      <c r="E52" s="32" t="n">
         <v>10200</v>
       </c>
-      <c r="J51" s="42" t="n">
+      <c r="J52" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="48" t="inlineStr">
-        <is>
-          <t>▍ G. 注意股 (資料日 20260626)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+    <row r="54" ht="22" customHeight="1">
       <c r="B54" s="49" t="inlineStr">
         <is>
+          <t>▍ G. 注意股 (資料日 20260701)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="50" t="inlineStr">
+        <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C54" s="49" t="inlineStr">
+      <c r="C55" s="50" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D54" s="49" t="inlineStr">
+      <c r="D55" s="50" t="inlineStr">
         <is>
           <t>累計次數</t>
         </is>
       </c>
-      <c r="E54" s="49" t="inlineStr">
+      <c r="E55" s="50" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="F54" s="49" t="inlineStr">
+      <c r="F55" s="50" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>040649</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>力積電統一6A購03</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>059570</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>強茂凱基5B購03</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="E56" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="50" t="inlineStr">
-        <is>
-          <t>050307</t>
-        </is>
-      </c>
-      <c r="C56" s="50" t="inlineStr">
-        <is>
-          <t>亞航國泰57購01</t>
-        </is>
-      </c>
-      <c r="D56" s="50" t="n">
+    <row r="57">
+      <c r="B57" s="51" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="C57" s="51" t="inlineStr">
+        <is>
+          <t>中福</t>
+        </is>
+      </c>
+      <c r="D57" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="50" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="F56" s="50" t="inlineStr">
+      <c r="E57" s="51" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="F57" s="51" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>059570</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>強茂凱基5B購03</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="E58" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="50" t="inlineStr">
-        <is>
-          <t>085788</t>
-        </is>
-      </c>
-      <c r="C58" s="50" t="inlineStr">
-        <is>
-          <t>T50反1中信5C購01</t>
-        </is>
-      </c>
-      <c r="D58" s="50" t="n">
+    <row r="59">
+      <c r="B59" s="51" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="C59" s="51" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="F58" s="50" t="inlineStr">
+      <c r="E59" s="51" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F59" s="51" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>中福</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>榮星</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="E60" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>25.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="51" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="C61" s="51" t="inlineStr">
+        <is>
+          <t>東聯</t>
+        </is>
+      </c>
+      <c r="D61" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="51" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F61" s="51" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="50" t="inlineStr">
-        <is>
-          <t>2233</t>
-        </is>
-      </c>
-      <c r="C60" s="50" t="inlineStr">
-        <is>
-          <t>宇隆</t>
-        </is>
-      </c>
-      <c r="D60" s="50" t="n">
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>中纖</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="50" t="n">
-        <v>214</v>
-      </c>
-      <c r="F60" s="50" t="inlineStr">
-        <is>
-          <t>34.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
+      <c r="E62" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>51.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>宏旭-KY</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="n">
-        <v>2035</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>64.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="50" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="C62" s="50" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="D62" s="50" t="n">
+      <c r="E63" s="51" t="n">
+        <v>62</v>
+      </c>
+      <c r="F63" s="51" t="inlineStr">
+        <is>
+          <t>24.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="50" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F62" s="50" t="inlineStr">
-        <is>
-          <t>53.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
+      <c r="E64" t="n">
+        <v>169</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>42.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="C65" s="51" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="n">
-        <v>3880</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>61.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="50" t="inlineStr">
-        <is>
-          <t>2483</t>
-        </is>
-      </c>
-      <c r="C64" s="50" t="inlineStr">
-        <is>
-          <t>百容</t>
-        </is>
-      </c>
-      <c r="D64" s="50" t="n">
+      <c r="E65" s="51" t="n">
+        <v>2660</v>
+      </c>
+      <c r="F65" s="51" t="inlineStr">
+        <is>
+          <t>50.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>矽統</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="50" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="F64" s="50" t="inlineStr">
-        <is>
-          <t>60.54</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
+      <c r="E66" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>43.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>凱美</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="n">
-        <v>4720</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>29.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="50" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="C66" s="50" t="inlineStr">
-        <is>
-          <t>禾伸堂</t>
-        </is>
-      </c>
-      <c r="D66" s="50" t="n">
+      <c r="E67" s="51" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="F67" s="51" t="inlineStr">
+        <is>
+          <t>70.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>國碩</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="50" t="n">
-        <v>729</v>
-      </c>
-      <c r="F66" s="50" t="inlineStr">
-        <is>
-          <t>93.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>正達</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
+      <c r="E68" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-----</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>希華</t>
+        </is>
+      </c>
+      <c r="D69" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="50" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="C68" s="50" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="D68" s="50" t="n">
+      <c r="E69" s="51" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="F69" s="51" t="inlineStr">
+        <is>
+          <t>107.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>信邦</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="50" t="n">
-        <v>4420</v>
-      </c>
-      <c r="F68" s="50" t="inlineStr">
-        <is>
-          <t>132.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
-        <v>530</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>157.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260626)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="11" t="inlineStr">
+      <c r="E70" t="n">
+        <v>333</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260701)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>借券張數</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>融券張數</t>
         </is>
       </c>
-      <c r="F72" s="11" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>81854</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>2430</v>
-      </c>
-      <c r="F73" s="51" t="n">
-        <v>33.68</v>
-      </c>
-    </row>
     <row r="74">
-      <c r="B74" s="50" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="C74" s="50" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="D74" s="52" t="n">
-        <v>15421</v>
-      </c>
-      <c r="E74" s="52" t="n">
-        <v>3653</v>
+      <c r="B74" s="52" t="inlineStr">
+        <is>
+          <t>🔴 2887</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>13846</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="F74" s="53" t="n">
-        <v>4.22</v>
+        <v>4615.33</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="54" t="inlineStr">
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D75" s="54" t="n">
+        <v>12974</v>
+      </c>
+      <c r="E75" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>11153</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>🔴 3231</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" s="51" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>
       </c>
-      <c r="D75" s="31" t="n">
-        <v>12666</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="F75" s="55" t="n">
-        <v>1151.45</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="50" t="inlineStr">
+      <c r="D77" s="54" t="n">
+        <v>11039</v>
+      </c>
+      <c r="E77" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="56" t="n">
+        <v>3679.67</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="52" t="inlineStr">
+        <is>
+          <t>🔴 2002</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>8477</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="53" t="n">
+        <v>1695.4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="51" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C79" s="51" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D79" s="54" t="n">
+        <v>7892</v>
+      </c>
+      <c r="E79" s="54" t="n">
+        <v>451</v>
+      </c>
+      <c r="F79" s="57" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>中纖</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>7786</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>437</v>
+      </c>
+      <c r="F80" s="58" t="n">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="55" t="inlineStr">
+        <is>
+          <t>🔴 1101</t>
+        </is>
+      </c>
+      <c r="C81" s="51" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="D81" s="54" t="n">
+        <v>7348</v>
+      </c>
+      <c r="E81" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="56" t="n">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="52" t="inlineStr">
+        <is>
+          <t>🔴 0056</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>7238</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="53" t="n">
+        <v>1809.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="D83" s="54" t="n">
+        <v>6334</v>
+      </c>
+      <c r="E83" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="52" t="inlineStr">
+        <is>
+          <t>🔴 2886</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>6035</v>
+      </c>
+      <c r="E84" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" s="53" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="51" t="inlineStr">
         <is>
           <t>2312</t>
         </is>
       </c>
-      <c r="C76" s="50" t="inlineStr">
+      <c r="C85" s="51" t="inlineStr">
         <is>
           <t>金寶</t>
         </is>
       </c>
-      <c r="D76" s="52" t="n">
-        <v>11071</v>
-      </c>
-      <c r="E76" s="52" t="n">
-        <v>71</v>
-      </c>
-      <c r="F76" s="53" t="n">
-        <v>155.93</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>9454</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>27</v>
-      </c>
-      <c r="F77" s="51" t="n">
-        <v>350.15</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="50" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C78" s="50" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D78" s="52" t="n">
-        <v>7555</v>
-      </c>
-      <c r="E78" s="52" t="n">
+      <c r="D85" s="54" t="n">
+        <v>5782</v>
+      </c>
+      <c r="E85" s="54" t="n">
+        <v>74</v>
+      </c>
+      <c r="F85" s="57" t="n">
+        <v>78.14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="n">
+        <v>5366</v>
+      </c>
+      <c r="E86" s="32" t="n">
+        <v>278</v>
+      </c>
+      <c r="F86" s="58" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>寶成</t>
+        </is>
+      </c>
+      <c r="D87" s="54" t="n">
+        <v>5179</v>
+      </c>
+      <c r="E87" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="50" t="inlineStr">
+      <c r="F87" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>7036</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>404</v>
-      </c>
-      <c r="F79" s="51" t="n">
-        <v>17.42</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="56" t="inlineStr">
-        <is>
-          <t>🔴 2002</t>
-        </is>
-      </c>
-      <c r="C80" s="50" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D80" s="52" t="n">
-        <v>6203</v>
-      </c>
-      <c r="E80" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="F80" s="57" t="n">
-        <v>1240.6</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>6176</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>730</v>
-      </c>
-      <c r="F81" s="51" t="n">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="50" t="inlineStr">
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>瑞軒</t>
+        </is>
+      </c>
+      <c r="D88" s="32" t="n">
+        <v>5112</v>
+      </c>
+      <c r="E88" s="32" t="n">
+        <v>602</v>
+      </c>
+      <c r="F88" s="58" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="B90" s="59" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 306 檔, 已剔除過期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="50" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C91" s="50" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="D91" s="50" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="E91" s="50" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F91" s="50" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="C82" s="50" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="D82" s="52" t="n">
-        <v>6020</v>
-      </c>
-      <c r="E82" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2371</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>大同</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>5946</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F83" s="51" t="n">
-        <v>743.25</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="56" t="inlineStr">
-        <is>
-          <t>🔴 2886</t>
-        </is>
-      </c>
-      <c r="C84" s="50" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D84" s="52" t="n">
-        <v>5830</v>
-      </c>
-      <c r="E84" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="57" t="n">
-        <v>5830</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="D85" s="31" t="n">
-        <v>5605</v>
-      </c>
-      <c r="E85" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="50" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C86" s="50" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D86" s="52" t="n">
-        <v>5580</v>
-      </c>
-      <c r="E86" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="54" t="inlineStr">
-        <is>
-          <t>🔴 2845</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>遠東銀</t>
-        </is>
-      </c>
-      <c r="D87" s="31" t="n">
-        <v>5502</v>
-      </c>
-      <c r="E87" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F87" s="55" t="n">
-        <v>1100.4</v>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="B89" s="58" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 263 檔, 已剔除過期)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="49" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C90" s="49" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D90" s="49" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E90" s="49" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F90" s="49" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>2.620556</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="50" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C92" s="50" t="inlineStr">
-        <is>
-          <t>3054</t>
-        </is>
-      </c>
-      <c r="D92" s="50" t="inlineStr">
-        <is>
-          <t>立萬利</t>
-        </is>
-      </c>
-      <c r="E92" s="50" t="inlineStr">
+      <c r="F92" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>1101B</t>
+        </is>
+      </c>
+      <c r="D93" s="51" t="inlineStr">
+        <is>
+          <t>台泥乙特</t>
+        </is>
+      </c>
+      <c r="E93" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F92" s="50" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>3669</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>圓展</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" s="51" t="n">
+        <v>2.02625</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>大統新創</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="50" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C94" s="50" t="inlineStr">
-        <is>
-          <t>3708</t>
-        </is>
-      </c>
-      <c r="D94" s="50" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="E94" s="50" t="inlineStr">
+      <c r="F94" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C95" s="51" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="D95" s="51" t="inlineStr">
+        <is>
+          <t>元禎</t>
+        </is>
+      </c>
+      <c r="E95" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F94" s="50" t="n">
-        <v>6.49582</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>弘凱</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" s="51" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>麗正</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="50" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C96" s="50" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="D96" s="50" t="inlineStr">
-        <is>
-          <t>志強-KY</t>
-        </is>
-      </c>
-      <c r="E96" s="50" t="inlineStr">
+      <c r="F96" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="D97" s="51" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="E97" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F96" s="50" t="n">
-        <v>5.155125</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>6789</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>采鈺</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" s="51" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="50" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C98" s="50" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="D98" s="50" t="inlineStr">
-        <is>
-          <t>黑松</t>
-        </is>
-      </c>
-      <c r="E98" s="50" t="inlineStr">
+      <c r="F98" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
+        <is>
+          <t>2881A</t>
+        </is>
+      </c>
+      <c r="D99" s="51" t="inlineStr">
+        <is>
+          <t>富邦特</t>
+        </is>
+      </c>
+      <c r="E99" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F98" s="50" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>三洋實業</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" s="51" t="n">
+        <v>2.74875</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2881B</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>富邦金乙特</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="50" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C100" s="50" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="D100" s="50" t="inlineStr">
-        <is>
-          <t>長興</t>
-        </is>
-      </c>
-      <c r="E100" s="50" t="inlineStr">
-        <is>
-          <t>權</t>
-        </is>
-      </c>
-      <c r="F100" s="50" t="n">
-        <v>0</v>
+      <c r="F100" t="n">
+        <v>2.572356</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>中再保</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
+        <is>
+          <t>2881C</t>
+        </is>
+      </c>
+      <c r="D101" s="51" t="inlineStr">
+        <is>
+          <t>富邦金丙特</t>
+        </is>
+      </c>
+      <c r="E101" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>2.2</v>
+      <c r="F101" s="51" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="50" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C102" s="50" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="D102" s="50" t="inlineStr">
-        <is>
-          <t>嘉晶</t>
-        </is>
-      </c>
-      <c r="E102" s="50" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F102" s="50" t="n">
-        <v>0.496874</v>
+      <c r="F102" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3563</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>牧德</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>2887E</t>
+        </is>
+      </c>
+      <c r="D103" s="51" t="inlineStr">
+        <is>
+          <t>台新新光戊特一</t>
+        </is>
+      </c>
+      <c r="E103" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>12</v>
+      <c r="F103" s="51" t="n">
+        <v>2.43625</v>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="50" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C104" s="50" t="inlineStr">
-        <is>
-          <t>4164</t>
-        </is>
-      </c>
-      <c r="D104" s="50" t="inlineStr">
-        <is>
-          <t>承業醫</t>
-        </is>
-      </c>
-      <c r="E104" s="50" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2887F</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>台新新光戊特二</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F104" s="50" t="n">
-        <v>1.107736</v>
+      <c r="F104" t="n">
+        <v>1.933601</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>致伸</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="B105" s="51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C105" s="51" t="inlineStr">
+        <is>
+          <t>2887G</t>
+        </is>
+      </c>
+      <c r="D105" s="51" t="inlineStr">
+        <is>
+          <t>台新新光庚特一</t>
+        </is>
+      </c>
+      <c r="E105" s="51" t="inlineStr">
         <is>
           <t>息</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>4.569244</v>
+      <c r="F105" s="51" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2887H</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>台新新光庚特二</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="G19:I19"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="B53:J53"/>
-    <mergeCell ref="B20:N20"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B37:J37"/>
     <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B22:N22"/>
     <mergeCell ref="B12:N12"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B41:J41"/>
     <mergeCell ref="B21:N21"/>
     <mergeCell ref="B11:N11"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B14:N14"/>
+    <mergeCell ref="B90:J90"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B71:J71"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B18:J18"/>
     <mergeCell ref="B10:N10"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <conditionalFormatting sqref="N15">
+  <conditionalFormatting sqref="N16">
     <cfRule type="dataBar" priority="1">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2850,7 +2867,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
+  <conditionalFormatting sqref="E16">
     <cfRule type="dataBar" priority="2">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2859,7 +2876,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:D29">
+  <conditionalFormatting sqref="D26:D30">
     <cfRule type="dataBar" priority="3">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2868,7 +2885,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H29">
+  <conditionalFormatting sqref="H26:H30">
     <cfRule type="dataBar" priority="4">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2877,7 +2894,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C42:C51">
+  <conditionalFormatting sqref="C43:C52">
     <cfRule type="dataBar" priority="5">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2886,7 +2903,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:J51">
+  <conditionalFormatting sqref="J43:J52">
     <cfRule type="dataBar" priority="6">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2895,7 +2912,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D55:D69">
+  <conditionalFormatting sqref="D56:D70">
     <cfRule type="dataBar" priority="7">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2904,7 +2921,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D73:D87">
+  <conditionalFormatting sqref="D74:D88">
     <cfRule type="dataBar" priority="8">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
@@ -2913,7 +2930,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F73:F87">
+  <conditionalFormatting sqref="F74:F88">
     <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
